--- a/error_models/conv_models/nv_32x32_b1_dat-1048576_wt-262144_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x32_b1_dat-1048576_wt-262144_int16/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,16 +682,16 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9889706056019654</v>
+        <v>0.9917287936175236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0110228636218764</v>
+        <v>0.008265945707051499</v>
       </c>
       <c r="I2" t="n">
-        <v>6.491500671682e-06</v>
+        <v>5.221399938290891e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7978859912370936</v>
+        <v>0.7978859912370937</v>
       </c>
       <c r="K2" t="n">
         <v>0.0342582220946479</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2038046535972707</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.7961953464027293</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -616,16 +824,16 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9922926067243356</v>
+        <v>0.9931315732147382</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0077001560415588</v>
+        <v>0.0068623186870505</v>
       </c>
       <c r="I3" t="n">
-        <v>7.197958619177764e-06</v>
+        <v>6.068822724383541e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.773220593213</v>
+        <v>0.7732205932129999</v>
       </c>
       <c r="K3" t="n">
         <v>0.0472825332075641</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0017590595516187</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2038045642577986</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.7961954357422013</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -680,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.998010949512538</v>
+        <v>0.9982536513556364</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0019813922448065</v>
+        <v>0.0017395685067157</v>
       </c>
       <c r="I4" t="n">
-        <v>7.618967168791137e-06</v>
+        <v>6.740862161045613e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.2610082301456455</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5541722650591234</v>
+        <v>0.5541722650591236</v>
       </c>
       <c r="L4" t="n">
         <v>0.0486769607133655</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>0.004415643885867</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.2038048504023643</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7961951495976357</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.9998317048111924</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0001682951888076</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9957807093593044</v>
+        <v>0.9959649206831248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0042117687820593</v>
+        <v>0.004028419709464</v>
       </c>
       <c r="I5" t="n">
-        <v>7.482583149353345e-06</v>
+        <v>6.620331924460751e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.2152659061884546</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5940598423120476</v>
+        <v>0.5940598423120477</v>
       </c>
       <c r="L5" t="n">
         <v>0.038264382350152</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0015536173509051</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2038049713879688</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.7961950286120312</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.9997451494938968</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.000254850506103</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -808,19 +1250,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9965852157841776</v>
+        <v>0.9967792374310016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0034071013881813</v>
+        <v>0.0032139579101239</v>
       </c>
       <c r="I6" t="n">
-        <v>7.643552154395476e-06</v>
+        <v>6.765383387748783e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.2226279642018477</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5922722664164872</v>
+        <v>0.5922722664164873</v>
       </c>
       <c r="L6" t="n">
         <v>0.048549971994866</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.005586672137033</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.2038125846998422</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.7961874153001579</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.9997452415789519</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0002547584210478</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9872498551022912</v>
+        <v>0.9924965696719256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0127428174623552</v>
+        <v>0.0074973445617031</v>
       </c>
       <c r="I7" t="n">
-        <v>7.288159866887955e-06</v>
+        <v>6.046490884709285e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.7937996002595055</v>
@@ -887,7 +1407,7 @@
         <v>0.0393785359802161</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06818156607930639</v>
+        <v>0.0681815660793065</v>
       </c>
       <c r="M7" t="n">
         <v>0.0019082687206494</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>5.705704126716885e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2038050640065925</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7961949359934074</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -936,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9935000172745718</v>
+        <v>0.9955199617927976</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0064927007815284</v>
+        <v>0.0044739181381543</v>
       </c>
       <c r="I8" t="n">
-        <v>7.242668412857491e-06</v>
+        <v>6.080793561596837e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7995276769684105</v>
+        <v>0.7995276769684106</v>
       </c>
       <c r="K8" t="n">
         <v>0.0219191849445622</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0042300933058766</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2038046621133326</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7961953378866674</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1000,19 +1676,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.996202890289462</v>
+        <v>0.9984626218873724</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0037887859037338</v>
+        <v>0.0015301720290669</v>
       </c>
       <c r="I9" t="n">
-        <v>8.284531317736524e-06</v>
+        <v>7.166808073991043e-06</v>
       </c>
       <c r="J9" t="n">
         <v>0.7997164049494392</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0372080893369758</v>
+        <v>0.0372080893369757</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1021,7 +1697,7 @@
         <v>0.0042984250134963</v>
       </c>
       <c r="N9" t="n">
-        <v>5.148672658373295e-06</v>
+        <v>5.148672658373296e-06</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>8.152048861106653e-06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.99964253088136</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.00035746911864</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1064,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9987926431663268</v>
+        <v>0.9989083725286384</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0011999154526657</v>
+        <v>0.0010849691567488</v>
       </c>
       <c r="I10" t="n">
-        <v>7.402105520729835e-06</v>
+        <v>6.619039126306914e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0560983244613025</v>
@@ -1104,6 +1858,84 @@
       </c>
       <c r="T10" t="n">
         <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9992752554955012</v>
+        <v>0.9995077350021226</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0007173345155997</v>
+        <v>0.0004857963559226</v>
       </c>
       <c r="I11" t="n">
-        <v>7.370713412573598e-06</v>
+        <v>6.429366468066549e-06</v>
       </c>
       <c r="J11" t="n">
         <v>0.0506616237558041</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8806485289935988</v>
+        <v>0.8806485289935989</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1149,7 +1981,7 @@
         <v>0.0013535032002125</v>
       </c>
       <c r="N11" t="n">
-        <v>4.854922828769863e-06</v>
+        <v>4.854922828769862e-06</v>
       </c>
       <c r="O11" t="n">
         <v>4.841971499516494e-08</v>
@@ -1168,6 +2000,84 @@
       </c>
       <c r="T11" t="n">
         <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9974305301211968</v>
+        <v>0.9985362723448262</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0025615922782928</v>
+        <v>0.0014567994334234</v>
       </c>
       <c r="I12" t="n">
-        <v>7.838325023650895e-06</v>
+        <v>6.888946263760824e-06</v>
       </c>
       <c r="J12" t="n">
         <v>0.6383059639217209</v>
@@ -1213,7 +2123,7 @@
         <v>0.0139636066362738</v>
       </c>
       <c r="N12" t="n">
-        <v>2.742653652553535e-06</v>
+        <v>2.742653652553536e-06</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>0.0012608435682709</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1256,16 +2244,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9983453507689316</v>
+        <v>0.9993786164909774</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0016465156800005</v>
+        <v>0.0006144121449374</v>
       </c>
       <c r="I13" t="n">
-        <v>8.094275581161245e-06</v>
+        <v>6.932088598404684e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5810347190587029</v>
+        <v>0.581034719058703</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1277,7 +2265,7 @@
         <v>0.0069552797440982</v>
       </c>
       <c r="N13" t="n">
-        <v>4.054859388321289e-06</v>
+        <v>4.054859388321288e-06</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>3.798249686446665e-06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9970043775924734</v>
+        <v>0.998109299275292</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0029876980880806</v>
+        <v>0.0018836290067503</v>
       </c>
       <c r="I14" t="n">
-        <v>7.88504395938792e-06</v>
+        <v>7.032442471001688e-06</v>
       </c>
       <c r="J14" t="n">
         <v>0.65145814575598</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>0.0013009646819503</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9981914972789454</v>
+        <v>0.9992826770005998</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0018004399200684</v>
+        <v>0.0007104005099851</v>
       </c>
       <c r="I15" t="n">
-        <v>8.02352549956588e-06</v>
+        <v>6.883213928370844e-06</v>
       </c>
       <c r="J15" t="n">
         <v>0.6929082076769468</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>2.284819500341868e-06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9992531523777451</v>
+        <v>0.9997228455839988</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0007392379878753</v>
+        <v>0.0002707466249534</v>
       </c>
       <c r="I16" t="n">
-        <v>7.570358893211376e-06</v>
+        <v>6.36851556109224e-06</v>
       </c>
       <c r="J16" t="n">
         <v>0.2908946636582669</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>6.064818443385388e-06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9984951871728256</v>
+        <v>0.9988584895546104</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0014971756638169</v>
+        <v>0.0011347049721049</v>
       </c>
       <c r="I17" t="n">
-        <v>7.597887870940728e-06</v>
+        <v>6.766197797864028e-06</v>
       </c>
       <c r="J17" t="n">
         <v>0.1954676707900978</v>
@@ -1533,13 +2833,13 @@
         <v>0.0194532211672224</v>
       </c>
       <c r="N17" t="n">
-        <v>4.656146891960978e-06</v>
+        <v>4.656146891960977e-06</v>
       </c>
       <c r="O17" t="n">
         <v>1.082513756113176e-08</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6102994049924769</v>
+        <v>0.6102994049924771</v>
       </c>
       <c r="Q17" t="n">
         <v>0.1577070453995316</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0056726411108817</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9992917832047687</v>
+        <v>0.9997299331731672</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0007008065824393</v>
+        <v>0.0002638455049735</v>
       </c>
       <c r="I18" t="n">
-        <v>7.370937305236874e-06</v>
+        <v>6.182046372594724e-06</v>
       </c>
       <c r="J18" t="n">
         <v>0.1854008593169519</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>0.0017991446218601</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1640,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9990143953391476</v>
+        <v>0.9991649406935246</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0009781936389046</v>
+        <v>0.0008284892480808</v>
       </c>
       <c r="I19" t="n">
-        <v>7.371746461177839e-06</v>
+        <v>6.530782907946058e-06</v>
       </c>
       <c r="J19" t="n">
         <v>0.0518254032675626</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7758218297411685</v>
+        <v>0.7758218297411684</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1680,6 +3136,84 @@
       </c>
       <c r="T19" t="n">
         <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1704,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9994220409710276</v>
+        <v>0.9996319310764792</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0005707040307514</v>
+        <v>0.0003618418433002</v>
       </c>
       <c r="I20" t="n">
-        <v>7.215722734435094e-06</v>
+        <v>6.187804733951743e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0804913508726831</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8413310759894745</v>
+        <v>0.8413310759894747</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1744,6 +3278,84 @@
       </c>
       <c r="T20" t="n">
         <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1768,19 +3380,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9985586961316532</v>
+        <v>0.9986881731796532</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0014337471885099</v>
+        <v>0.0013050397813316</v>
       </c>
       <c r="I21" t="n">
-        <v>7.517404350405028e-06</v>
+        <v>6.747763528533695e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0125351530593683</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8330919879565584</v>
+        <v>0.8330919879565583</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1789,10 +3401,10 @@
         <v>0.0034698904376652</v>
       </c>
       <c r="N21" t="n">
-        <v>4.562573362364761e-06</v>
+        <v>4.56257336236476e-06</v>
       </c>
       <c r="O21" t="n">
-        <v>3.196772453934242e-07</v>
+        <v>3.196772453934241e-07</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -1808,6 +3420,84 @@
       </c>
       <c r="T21" t="n">
         <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1832,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0927725671721782</v>
+        <v>0.604888483897514</v>
       </c>
       <c r="H22" t="n">
-        <v>0.907219627120424</v>
+        <v>0.3951045046774196</v>
       </c>
       <c r="I22" t="n">
-        <v>7.766431911090382e-06</v>
+        <v>6.972149579693938e-06</v>
       </c>
       <c r="J22" t="n">
         <v>0.0030862840377819</v>
@@ -1850,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.79914968814316e-05</v>
+        <v>1.799149688143159e-05</v>
       </c>
       <c r="N22" t="n">
         <v>4.916987034229967e-08</v>
@@ -1872,6 +3562,84 @@
       </c>
       <c r="T22" t="n">
         <v>1.074209729039396e-07</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.97513654513633</v>
+        <v>0.9802745022772404</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0248557038587491</v>
+        <v>0.0197185032006891</v>
       </c>
       <c r="I23" t="n">
-        <v>7.711729434333895e-06</v>
+        <v>6.955246583815636e-06</v>
       </c>
       <c r="J23" t="n">
         <v>0.7973247842385122</v>
@@ -1926,7 +3694,7 @@
         <v>2.024967511490917e-06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1611630330697803</v>
+        <v>0.1611630330697802</v>
       </c>
       <c r="R23" t="n">
         <v>1.514790486364797e-05</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>0.0006914576218349</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1960,16 +3806,16 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.995523202372666</v>
+        <v>0.9967815706891708</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0044690238442803</v>
+        <v>0.0032114567988685</v>
       </c>
       <c r="I24" t="n">
-        <v>7.734507566866179e-06</v>
+        <v>6.933236473926508e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6483200823148439</v>
+        <v>0.6483200823148438</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1987,7 +3833,7 @@
         <v>4.399520835264485e-09</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1463870693653018</v>
+        <v>0.1463870693653019</v>
       </c>
       <c r="Q24" t="n">
         <v>0.1648338071336713</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>0.0008066902056405</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9969751932073828</v>
+        <v>0.9974570195712702</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0030169978132441</v>
+        <v>0.0025359240610014</v>
       </c>
       <c r="I25" t="n">
-        <v>7.769703886327388e-06</v>
+        <v>7.017092241668248e-06</v>
       </c>
       <c r="J25" t="n">
         <v>0.3906187982815695</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.002585473179633</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9979546106357288</v>
+        <v>0.9981384158124228</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0020380014013033</v>
+        <v>0.0018550231417605</v>
       </c>
       <c r="I26" t="n">
-        <v>7.348687480831091e-06</v>
+        <v>6.521770330111876e-06</v>
       </c>
       <c r="J26" t="n">
         <v>0.1969325715472674</v>
@@ -2115,7 +4117,7 @@
         <v>0.0380171701837328</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6007016847675816</v>
+        <v>0.6007016847675815</v>
       </c>
       <c r="Q26" t="n">
         <v>0.0064321945664297</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0053150231652568</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2038048845449316</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.7961951154550684</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.999752021767461</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.000247978232539</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9924404925203556</v>
+        <v>0.9939705521167777</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0075521883872385</v>
+        <v>0.0060232693683185</v>
       </c>
       <c r="I27" t="n">
-        <v>7.27981691922481e-06</v>
+        <v>6.139239417050485e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.7875474943904576</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0037276292941371</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.2038047591618447</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.7961952408381553</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.996628068215386</v>
+        <v>0.997043496635484</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0033645514123934</v>
+        <v>0.0029501069424845</v>
       </c>
       <c r="I28" t="n">
-        <v>7.341096733957728e-06</v>
+        <v>6.357146544957444e-06</v>
       </c>
       <c r="J28" t="n">
         <v>0.4857203609147815</v>
@@ -2243,7 +4401,7 @@
         <v>0.0434732294063533</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3135697397731331</v>
+        <v>0.3135697397731332</v>
       </c>
       <c r="Q28" t="n">
         <v>0.0023760732153247</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0051608818082542</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9928332451972126</v>
+        <v>0.9933099506640108</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0071593160652845</v>
+        <v>0.0066835968875035</v>
       </c>
       <c r="I29" t="n">
-        <v>7.399462016126589e-06</v>
+        <v>6.413172999213265e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.5329726635101865</v>
@@ -2295,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07458836307976149</v>
+        <v>0.0745883630797616</v>
       </c>
       <c r="M29" t="n">
         <v>0.0312303181850703</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0087882027839273</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.999640117507592</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0.0003598824924079</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2344,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09249931040245959</v>
+        <v>0.605161778305807</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9074927219812448</v>
+        <v>0.394831046132546</v>
       </c>
       <c r="I30" t="n">
-        <v>7.928340808827778e-06</v>
+        <v>7.136286160455185e-06</v>
       </c>
       <c r="J30" t="n">
         <v>0.0030291818460793</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9927950779261122</v>
+        <v>0.992795077926112</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2384,6 +4698,84 @@
       </c>
       <c r="T30" t="n">
         <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2408,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9931420311003948</v>
+        <v>0.9955787964110804</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0068498063801815</v>
+        <v>0.0044138775536302</v>
       </c>
       <c r="I31" t="n">
-        <v>8.123243937114889e-06</v>
+        <v>7.28675980276932e-06</v>
       </c>
       <c r="J31" t="n">
         <v>0.1994223042596453</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>1.701351890656476e-06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9859812090017188</v>
+        <v>0.9891815082020762</v>
       </c>
       <c r="H32" t="n">
-        <v>0.014010938318808</v>
+        <v>0.010811412055019</v>
       </c>
       <c r="I32" t="n">
-        <v>7.81340398673048e-06</v>
+        <v>7.040467418148857e-06</v>
       </c>
       <c r="J32" t="n">
         <v>0.2981197168828265</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2536,19 +5084,19 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9740603579693834</v>
+        <v>0.9755691216307384</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0259330232855019</v>
+        <v>0.0244255104074985</v>
       </c>
       <c r="I33" t="n">
-        <v>6.579469627795678e-06</v>
+        <v>5.328686276429687e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.3754781815523152</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4180382539552467</v>
+        <v>0.4180382539552466</v>
       </c>
       <c r="L33" t="n">
         <v>2.685964320532498e-06</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.0024281547604642</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2600,19 +5226,19 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9647902650841166</v>
+        <v>0.967344851120302</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0352029630396173</v>
+        <v>0.0326496430258419</v>
       </c>
       <c r="I34" t="n">
-        <v>6.732600779521002e-06</v>
+        <v>5.466578369285107e-06</v>
       </c>
       <c r="J34" t="n">
         <v>0.3906189074993884</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4029389819300174</v>
+        <v>0.4029389819300175</v>
       </c>
       <c r="L34" t="n">
         <v>2.02930464262095e-06</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>0.0034374763824829</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9851409899310186</v>
+        <v>0.9913372177516189</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0148517492672266</v>
+        <v>0.008656742764412251</v>
       </c>
       <c r="I35" t="n">
-        <v>7.221526267943708e-06</v>
+        <v>6.000208482227765e-06</v>
       </c>
       <c r="J35" t="n">
         <v>0.7938342272637453</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>0.001584499852651216</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.2038046466466327</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.7961953533533673</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2728,16 +5510,16 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9662081856515536</v>
+        <v>0.9750070062304974</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03378463352743575</v>
+        <v>0.0249870222270306</v>
       </c>
       <c r="I36" t="n">
-        <v>7.141545523915013e-06</v>
+        <v>5.932266985446313e-06</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7962414077560503</v>
+        <v>0.7962414077560502</v>
       </c>
       <c r="K36" t="n">
         <v>0.01742956352090025</v>
@@ -2749,7 +5531,7 @@
         <v>0.02361429638312225</v>
       </c>
       <c r="N36" t="n">
-        <v>0.03377073761358455</v>
+        <v>0.0337707376135845</v>
       </c>
       <c r="O36" t="n">
         <v>0.0328525798953982</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>0.00187181831744435</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.00596593628386565</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.9940340637161342</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2792,16 +5652,16 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9855980455941777</v>
+        <v>0.9879725439564276</v>
       </c>
       <c r="H37" t="n">
-        <v>0.01439466844953045</v>
+        <v>0.0120212917096073</v>
       </c>
       <c r="I37" t="n">
-        <v>7.246680805059892e-06</v>
+        <v>6.125058478363963e-06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7950853320059109</v>
+        <v>0.795085332005911</v>
       </c>
       <c r="K37" t="n">
         <v>0.0057726005771086</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0024509006079085</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.753537392361294e-08</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.999999972464626</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9888241443730966</v>
+        <v>0.9895959220426478</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0111683339293131</v>
+        <v>0.01039754757226065</v>
       </c>
       <c r="I38" t="n">
-        <v>7.482422103753445e-06</v>
+        <v>6.49110960498585e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.6021828010849962</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.00192823744786325</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.5999124860485867</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0.4000875139514133</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,22 +5936,22 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9930493867529507</v>
+        <v>0.9933563578122309</v>
       </c>
       <c r="H39" t="n">
-        <v>0.006943135856147601</v>
+        <v>0.006636997914317826</v>
       </c>
       <c r="I39" t="n">
-        <v>7.438115415066151e-06</v>
+        <v>6.604997964639515e-06</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1643707402797438</v>
+        <v>0.1643707402797439</v>
       </c>
       <c r="K39" t="n">
         <v>0.2309714547460026</v>
       </c>
       <c r="L39" t="n">
-        <v>0.03443129055777758</v>
+        <v>0.03443129055777761</v>
       </c>
       <c r="M39" t="n">
         <v>0.0166403215608797</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.008328972143336175</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.1528536502358838</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.5971463497641163</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.5498164588924502</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0.2001835411075497</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9972432509541111</v>
+        <v>0.9973761131028749</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00274944690844235</v>
+        <v>0.0026174004269977</v>
       </c>
       <c r="I40" t="n">
-        <v>7.262861959908444e-06</v>
+        <v>6.447194640637457e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.1390751388644327</v>
@@ -3011,7 +6105,7 @@
         <v>0.07290246318490295</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3269913226374743</v>
+        <v>0.3269913226374742</v>
       </c>
       <c r="Q40" t="n">
         <v>0.0013878835558625</v>
@@ -3020,10 +6114,88 @@
         <v>0.00461562890778465</v>
       </c>
       <c r="S40" t="n">
-        <v>3.228196665393473e-05</v>
+        <v>3.228196665393472e-05</v>
       </c>
       <c r="T40" t="n">
         <v>0.00467678520432195</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.1019024846713985</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.3980975153286015</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.4997826329802089</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0.0002173670197911</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_32x32_b1_dat-1048576_wt-262144_int16/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x32_b1_dat-1048576_wt-262144_int16/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,330 +425,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9917287936175236</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.008265945707051499</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>5.221399938290891e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.7978859912370937</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0342582220946479</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0617796017235014</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0070774561114401</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0370686233381597</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0576572965379931</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.0041198835111617</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.0001455242956058</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.539118674231519e-06</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>5.773709774045294e-06</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.2038046535972707</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.7961953464027293</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -763,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
         <v>1</v>
@@ -778,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -787,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -799,98 +804,104 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9931315732147382</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0068623186870505</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>6.068822724383541e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.7732205932129999</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.0472825332075641</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.1094931462421788</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0155269559025208</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0244676626956312</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0260965550908342</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>2.305817311466161e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0017458823709055</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.0001534814271743</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0002517170163904</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0017590595516187</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.2038045642577986</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.7961954357422013</v>
       </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -905,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
         <v>1</v>
@@ -926,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -941,98 +952,104 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9982536513556364</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0017395685067157</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>6.740862161045613e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.2610082301456455</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.5541722650591236</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0486769607133655</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0161790288532871</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0486770763113872</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0599051476609902</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.468954436042302e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>5.50344211041411e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0027048013168222</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0004601570223388</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.004415643885867</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.2038048504023643</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.7961951495976357</v>
       </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1047,13 +1064,13 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
@@ -1062,17 +1079,17 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
         <v>0.9998317048111924</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>0.0001682951888076</v>
       </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
@@ -1083,98 +1100,104 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9959649206831248</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.004028419709464</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>6.620331924460751e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.2152659061884546</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.5940598423120477</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.038264382350152</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0252033091674677</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0620019706994827</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.054912785267088</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>9.85892837188696e-07</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0001071305522573</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0045978532522995</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0004895017577858</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0015536173509051</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.2038049713879688</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.7961950286120312</v>
       </c>
-      <c r="W5" t="n">
-        <v>1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1189,13 +1212,13 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
@@ -1204,17 +1227,17 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
         <v>0.9997451494938968</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AP5" t="n">
         <v>0.000254850506103</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
@@ -1225,98 +1248,104 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9967792374310016</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0032139579101239</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>6.765383387748783e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.2226279642018477</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.5922722664164873</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.048549971994866</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.017674435682378</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0581475403972136</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0460298989085125</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1.148449564182484e-06</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.0024753844399264</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0062508960686794</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.0003837472673321</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.005586672137033</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.2038125846998422</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.7961874153001579</v>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1331,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
         <v>1</v>
@@ -1346,17 +1375,17 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
         <v>0.9997452415789519</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AP6" t="n">
         <v>0.0002547584210478</v>
       </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
@@ -1367,98 +1396,104 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9924965696719256</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0074973445617031</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>6.046490884709285e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.7937996002595055</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0393785359802161</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.0681815660793065</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.0019082687206494</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0454492608085759</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0454442880333083</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>2.979414285853355e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0058301447369158</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>7.306176418982723e-07</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>4.015503695215706e-06</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>5.705704126716885e-07</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.2038050640065925</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.7961949359934074</v>
       </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1473,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
         <v>1</v>
@@ -1488,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1509,98 +1544,104 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9955199617927976</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0044739181381543</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>6.080793561596837e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.7995276769684106</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0219191849445622</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0401865850361305</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0192449545146592</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0381741811263955</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.058260529678474</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>2.16083094266101e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0101666663780771</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.0062471220378048</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3.173211162226152e-05</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0042300933058766</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.2038046621133326</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.7961953378866674</v>
       </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1615,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
         <v>1</v>
@@ -1630,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -1651,98 +1692,104 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9984626218873724</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0015301720290669</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>7.166808073991043e-06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.7997164049494392</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0372080893369757</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0042984250134963</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>5.148672658373296e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>4.358686312850075e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.158688301830833</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.498419128757088e-05</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>5.609599464905338e-05</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>8.152048861106653e-06</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1757,13 +1804,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -1772,17 +1819,17 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
         <v>0.99964253088136</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
         <v>0.00035746911864</v>
       </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
@@ -1793,72 +1840,78 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9989083725286384</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0010849691567488</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>6.619039126306914e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0560983244613025</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.7828902546958949</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0033744394855162</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>4.551320685658104e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>2.176580554081422e-07</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.1498221700972531</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0078100030058053</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
@@ -1866,13 +1919,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1902,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -1914,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -1923,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -1935,72 +1988,78 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9995077350021226</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0004857963559226</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>6.429366468066549e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0506616237558041</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.8806485289935989</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.0013535032002125</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>4.854922828769862e-06</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>4.841971499516494e-08</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0659513936942152</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0013800077381389</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
@@ -2008,13 +2067,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2044,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2056,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -2065,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2077,98 +2136,104 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9985362723448262</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0014567994334234</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>6.888946263760824e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.6383059639217209</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.450210989428645e-07</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.0139636066362738</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>2.742653652553536e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.1654503511159319</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.1558753161685163</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.697330182655153e-05</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0251038183372212</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.0012608435682709</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2183,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
         <v>1</v>
@@ -2204,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2219,98 +2284,104 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9993786164909774</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0006144121449374</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>6.932088598404684e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.581034719058703</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>7.582597727843467e-09</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.0069552797440982</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>4.054859388321288e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.2503046799679788</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1442445267971549</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>3.446563521385749e-05</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0174184288296922</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>3.798249686446665e-06</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2325,13 +2396,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
         <v>1</v>
@@ -2340,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2349,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -2361,98 +2432,104 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.998109299275292</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0018836290067503</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>7.032442471001688e-06</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.65145814575598</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0221092850682671</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>2.317923190758849e-06</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.14338834399054</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.1648593675132383</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>0.0013205372828557</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.015560998508491</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.0013009646819503</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2467,13 +2544,13 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="n">
         <v>1</v>
@@ -2482,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -2491,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -2503,98 +2580,104 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9992826770005998</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0007104005099851</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>6.883213928370844e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.6929082076769468</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0052303683096824</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>3.547664981799664e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.133882909097624</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1521838345458856</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>3.51520828997154e-05</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0157536565269926</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>2.284819500341868e-06</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2609,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
         <v>1</v>
@@ -2624,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -2633,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -2645,98 +2728,104 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9997228455839988</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.0002707466249534</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>6.36851556109224e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.2908946636582669</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0019221001331023</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>2.428562600666252e-06</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0001259422341199</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>5.462715976498796e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.6110461040464863</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0600042916717788</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.0019329166927271</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0340599861910113</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>6.064818443385388e-06</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2751,13 +2840,13 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -2766,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -2775,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -2787,98 +2876,104 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9988584895546104</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0011347049721049</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>6.766197797864028e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.1954676707900978</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0023693501251986</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>5.954189658657962e-06</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.0194532211672224</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>4.656146891960977e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>1.082513756113176e-08</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.6102994049924771</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.1577070453995316</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0019383450416466</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0070816609357691</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0056726411108817</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2893,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -2914,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -2929,98 +3024,104 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9997299331731672</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0002638455049735</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>6.182046372594724e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.1854008593169519</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0036243670590908</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>6.658625554384255e-09</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.0054963018040019</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>4.902739010117914e-06</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>1.634662319718888e-09</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.7127361752085155</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.0618692166273852</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.0018432509694477</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0272257340849621</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.0017991446218601</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3035,13 +3136,13 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
         <v>1</v>
@@ -3050,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -3059,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3071,72 +3172,78 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9991649406935246</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0008284892480808</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>6.530782907946058e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0518254032675626</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.7758218297411684</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.002768517321857</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>4.742976284777559e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>1.285724427221806e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.164833692512002</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.004745762048394</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -3144,13 +3251,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3180,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -3192,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3201,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -3213,72 +3320,78 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9996319310764792</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0003618418433002</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>6.187804733951743e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0804913508726831</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.8413310759894747</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.003219041300461</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>4.830141142041935e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>6.339557904949792e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.07331608689882529</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.0016375121263482</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -3286,13 +3399,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3322,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -3334,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
@@ -3343,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -3355,72 +3468,78 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9986881731796532</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0013050397813316</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>6.747763528533695e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0125351530593683</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.8330919879565583</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0034698904376652</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>4.56257336236476e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>3.196772453934241e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.14280597230012</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0080920747201936</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -3428,13 +3547,13 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3464,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
@@ -3476,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -3485,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -3497,98 +3616,104 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.604888483897514</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3951045046774196</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>6.972149579693938e-06</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0030862840377819</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9932056075436418</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>1.799149688143159e-05</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>4.916987034229967e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.935572810898942e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0036895859136196</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>3.841749592606767e-11</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>3.157475993775661e-07</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>1.074209729039396e-07</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3603,22 +3728,22 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -3627,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -3639,98 +3764,104 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.9802745022772404</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.0197185032006891</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>6.955246583815636e-06</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.7973247842385122</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0104835513871015</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>2.258878995592617e-07</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.0303045424825028</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>2.533603969273546e-06</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.024967511490917e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.1611630330697802</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>1.514790486364797e-05</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>1.265956053750152e-05</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.0006914576218349</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3745,13 +3876,13 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" t="n">
         <v>1</v>
@@ -3760,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -3769,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -3781,98 +3912,104 @@
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9967815706891708</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0032114567988685</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>6.933236473926508e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.6483200823148438</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>8.948268996422175e-07</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.0320327817478499</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2.126110531998886e-06</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>4.399520835264485e-09</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.1463870693653019</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1648338071336713</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>3.197265643699939e-05</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0075845319638161</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.0008066902056405</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3887,13 +4024,13 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -3902,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -3911,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -3923,78 +4060,84 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9974570195712702</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0025359240610014</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>7.017092241668248e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.3906187982815695</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0037742213414844</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.0003021154614132</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0289897188833515</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>4.70048612273185e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>1.101593679930224e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.4116166965708412</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1585836169960398</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0026110605509612</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0009135578715027</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.002585473179633</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -4002,19 +4145,19 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4029,13 +4172,13 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4050,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -4065,98 +4208,104 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9981384158124228</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0018550231417605</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>6.521770330111876e-06</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.1969325715472674</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0038494396610864</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0359570852188776</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.019790399739763</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0887078041327669</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0380171701837328</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.6007016847675815</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.0064321945664297</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0025198812886681</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0017767064530826</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0053150231652568</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.2038048845449316</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.7961951154550684</v>
       </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4171,13 +4320,13 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
         <v>1</v>
@@ -4186,17 +4335,17 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
         <v>0.999752021767461</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AP26" t="n">
         <v>0.000247978232539</v>
       </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ26" t="n">
         <v>0</v>
       </c>
@@ -4207,98 +4356,104 @@
         <v>0</v>
       </c>
       <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9939705521167777</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0060232693683185</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>6.139239417050485e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.7875474943904576</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.0355995001300101</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.0648379602487594</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0199175188747942</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0340128318406669</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0425131748507192</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>2.134930444883717e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0086088465832432</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.0010802537454984</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>2.693026787214037e-05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0037276292941371</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.2038047591618447</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.7961952408381553</v>
       </c>
-      <c r="W27" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4313,13 +4468,13 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
         <v>1</v>
@@ -4328,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -4349,98 +4504,104 @@
         <v>0</v>
       </c>
       <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.997043496635484</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0029501069424845</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>6.357146544957444e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.4857203609147815</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.075508056365632</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.022982905091125</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0343239815023288</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0434732294063533</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.3135697397731332</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.0023760732153247</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>1.121249893662435e-05</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.016873378410852</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0051608818082542</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4455,13 +4616,13 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
         <v>1</v>
@@ -4470,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -4491,98 +4652,104 @@
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9933099506640108</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0066835968875035</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>6.413172999213265e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.5329726635101865</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0745883630797616</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0312303181850703</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0315171902868603</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0386781199564484</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.2715042074523058</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.0029902457282822</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0024446128395491</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0024210782163908</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0087882027839273</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.2</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.8</v>
       </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4597,13 +4764,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
         <v>1</v>
@@ -4612,17 +4779,17 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
         <v>0.999640117507592</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AP29" t="n">
         <v>0.0003598824924079</v>
       </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ29" t="n">
         <v>0</v>
       </c>
@@ -4633,72 +4800,78 @@
         <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.605161778305807</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.394831046132546</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>7.136286160455185e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0030291818460793</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.992795077926112</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>6.541784942675895e-05</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>3.773669188617194e-07</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>2.248370078316238e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0041088471040066</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>1.036148268838009e-06</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
@@ -4706,13 +4879,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4739,22 +4912,22 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -4763,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -4775,98 +4948,104 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9955787964110804</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0044138775536302</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>7.28675980276932e-06</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.1994223042596453</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.6102621122687166</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>4.683867160122144e-08</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.0321295862954847</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>3.484361883215246e-05</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>2.644493164007134e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.158127997834748</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.701574204732047e-05</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>1.708021312920929e-06</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>1.701351890656476e-06</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4881,13 +5060,13 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
         <v>1</v>
@@ -4896,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
         <v>0</v>
@@ -4905,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
@@ -4917,98 +5096,104 @@
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9891815082020762</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.010811412055019</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>7.040467418148857e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.2981197168828265</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.5049224621262901</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>1.275850931959661e-07</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.0318911420847821</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>3.587887001166042e-05</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.878797876243461e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.1649869996827351</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.169041684612567e-05</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>3.006427805221451e-05</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5023,13 +5208,13 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="n">
         <v>1</v>
@@ -5038,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
@@ -5047,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
@@ -5059,98 +5244,104 @@
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.9755691216307384</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0244255104074985</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>5.328686276429687e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.3754781815523152</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.4180382539552466</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>2.685964320532498e-06</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0415977753278575</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.1575116605313555</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.837076649543932e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.0049040277233483</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>2.055651489075398e-05</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>1.682731806494694e-05</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.0024281547604642</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5165,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
         <v>1</v>
@@ -5180,10 +5371,10 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -5201,98 +5392,104 @@
         <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.967344851120302</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.0326496430258419</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>5.466578369285107e-06</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.3906189074993884</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.4029389819300175</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>2.02930464262095e-06</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.0415332113160635</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.154483309830596</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>5.735297094323851e-07</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2.339259564565535e-06</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.0069577286194291</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>2.358034629346182e-05</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>1.822706325705976e-06</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.0034374763824829</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5307,13 +5504,13 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
         <v>1</v>
@@ -5322,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -5343,98 +5540,104 @@
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9913372177516189</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.008656742764412251</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>6.000208482227765e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.7938342272637453</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.0208344525858123</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.06860395680223245</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.007821886949886801</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.0702430960724295</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.01715997032271295</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.894637897534449e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.01991200457568585</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.418708701627275e-06</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>2.552952757485623e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.001584499852651216</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.2038046466466327</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.7961953533533673</v>
       </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5449,13 +5652,13 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" t="n">
         <v>1</v>
@@ -5464,10 +5667,10 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -5485,98 +5688,104 @@
         <v>0</v>
       </c>
       <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9750070062304974</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0249870222270306</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>5.932266985446313e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.7962414077560502</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.01742956352090025</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.08058448374421445</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.02361429638312225</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.0337707376135845</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.0328525798953982</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>1.578781999721175e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.0116861989810767</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.0008870705523407</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>1.099468420336404e-05</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.00187181831744435</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.00596593628386565</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.9940340637161342</v>
       </c>
-      <c r="W36" t="n">
-        <v>1</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5591,13 +5800,13 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
         <v>1</v>
@@ -5606,10 +5815,10 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -5627,98 +5836,104 @@
         <v>0</v>
       </c>
       <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9879725439564276</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.0120212917096073</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>6.125058478363963e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.795085332005911</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.0057726005771086</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.08861871864344439</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.03473782248509415</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.0335893229229884</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.03111894384469775</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>2.09297195882635e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.008145404755659899</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.00014242328612095</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>1.462713202530508e-05</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0024509006079085</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>2.753537392361294e-08</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.999999972464626</v>
       </c>
-      <c r="W37" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5733,13 +5948,13 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
@@ -5748,10 +5963,10 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -5769,98 +5984,104 @@
         <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9895959220426478</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.01039754757226065</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>6.49110960498585e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.6021828010849962</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.07559805777272695</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.0359463169357095</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.04115363526936985</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.03992198726893055</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.1942947085856449</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.0030470837795704</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0010767452058009</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.00375211288611015</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.00192823744786325</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.1</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.9</v>
       </c>
-      <c r="W38" t="n">
-        <v>1</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5875,13 +6096,13 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" t="n">
         <v>1</v>
@@ -5890,17 +6111,17 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
         <v>0.5999124860485867</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AP38" t="n">
         <v>0.4000875139514133</v>
       </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ38" t="n">
         <v>0</v>
       </c>
@@ -5911,99 +6132,105 @@
         <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9933563578122309</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.006636997914317826</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>6.604997964639515e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.1643707402797439</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2309714547460026</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.03443129055777761</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.0166403215608797</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.04194642610638009</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.05171649418533698</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.4453755415195763</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.001487985552201382</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.00444208822175665</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.0002886458515216236</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.008328972143336175</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1528536502358838</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.5971463497641163</v>
       </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
       </c>
       <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
       <c r="AD39" t="n">
         <v>0</v>
       </c>
@@ -6017,14 +6244,14 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
         <v>1</v>
       </c>
@@ -6032,17 +6259,17 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
         <v>0.5498164588924502</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AP39" t="n">
         <v>0.2001835411075497</v>
       </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ39" t="n">
         <v>0</v>
       </c>
@@ -6053,99 +6280,105 @@
         <v>0</v>
       </c>
       <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9973761131028749</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0026174004269977</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>6.447194640637457e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.1390751388644327</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.3765331590401474</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.01769870231468565</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.009915381790759899</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.0448427085285734</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.07290246318490295</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.3269913226374742</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.0013878835558625</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00461562890778465</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>3.228196665393472e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.00467678520432195</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.1019024846713985</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.3980975153286015</v>
       </c>
-      <c r="W40" t="n">
-        <v>1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
       <c r="AD40" t="n">
         <v>0</v>
       </c>
@@ -6159,14 +6392,14 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
       <c r="AK40" t="n">
         <v>1</v>
       </c>
@@ -6174,17 +6407,17 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
         <v>0.4997826329802089</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AP40" t="n">
         <v>0.0002173670197911</v>
       </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ40" t="n">
         <v>0</v>
       </c>
@@ -6195,6 +6428,12 @@
         <v>0</v>
       </c>
       <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>1</v>
       </c>
     </row>
